--- a/reports/2026-08-20-tiger-space-etf-weekly.xlsx
+++ b/reports/2026-08-20-tiger-space-etf-weekly.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주간리포트" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주간보고서" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,9 +18,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="+0.00%;-0.00%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,54 +29,36 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Noto Sans KR"/>
       <b val="1"/>
-      <sz val="14"/>
+      <sz val="20"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
+      <name val="Noto Sans KR"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
+      <name val="Noto Sans KR"/>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Noto Sans KR"/>
       <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="000070C0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00555555"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Noto Sans KR"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Noto Sans KR"/>
       <i val="1"/>
-      <color rgb="00777777"/>
+      <color rgb="00595959"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -104,50 +86,60 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -155,15 +147,15 @@
   <dxfs count="2">
     <dxf>
       <font>
-        <name val="Arial"/>
-        <color rgb="00C00000"/>
+        <name val="Noto Sans KR"/>
+        <color rgb="00FF0000"/>
         <sz val="10"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <name val="Arial"/>
-        <color rgb="000070C0"/>
+        <name val="Noto Sans KR"/>
+        <color rgb="000000FF"/>
         <sz val="10"/>
       </font>
     </dxf>
@@ -529,377 +521,335 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>TIGER 미국우주테크 ETF (0183J0) 주간 보고서</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>보고서 기준일자: 2026-08-20  |  주가 기준일: 2026-08-19 (최근 종가) 대비 5거래일 전  |  편입종목 비중 기준일: 2026-07-31 (미래에셋자산운용 월간 팩트시트, 최신 공개본)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>보고서 기준일자: 2026-08-20 | 주가 기준일: 2026-08-19 종가, 2026-08-12 종가 대비 5거래일 전 | 편입종목 비중 기준일: 2026-07-31 (월간운용보고서/FactSheet 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>※ 참고: 요청하신 정식 명칭 "TIGER 미국우주테크&amp;방산iSelect"와 일치하는 종목을 tigeretf.com/네이버증권에서 확인하지 못해, 종목명·특징이 가장 근접한 "TIGER 미국우주테크"(0183J0, 미래에셋자산운용, KRX 상장, 미국 상장 우주기업 10종목 편입)를 기준으로 작성했습니다. 정식 명칭 확인 필요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>※ 일별(daily) 자산구성내역(PDF/CU) 페이지는 접근이 제한되어, 가장 최신 공개된 월간 팩트시트(2026-07-31 기준) 상위 10종목 비중을 사용했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>이번 주 상승 상위: Intuitive Machines Inc(LUNR) +9.26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>이번 주 하락 상위 3: AST SpaceMobile Inc(ASTS) -10.60%, Voyager Technologies Inc(VOYG) -9.65%, MDA Space Ltd(MDA) -8.98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
+          <t>이번 주 상승 상위: Intuitive Machines(LUNR) +9.26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>이번 주 하락 상위 3개: AST SpaceMobile(ASTS) -10.60%, Voyager Technologies(VOYG) -9.65%, MDA Space(MDA) -8.98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="8" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>비중(%)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>이번주 등락률(%)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>종가(USD)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>시가총액(억달러)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>주요 이슈</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Space Exploration Technologies Corp.</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>-0.044475</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>139.65</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>18408.4</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>글로벌스타·美우주군 위성 연속 발사(38분 간격 신기록), 2026년 100번째 미션 달성 등 팰컨9 발사 랠리 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>※ 조사 대상 10종목 중 상승 종목이 1개뿐이라 상승 상위는 해당 종목만 표기했습니다. (Intuitive Machines만 상승, 나머지 9종목은 이번 주 모두 하락)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>티커</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>비중(%)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>이번주 등락률(%)</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>종가(USD)</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>주요 이슈</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Space Exploration Technologies Corp (SpaceX)</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>SPCX</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>0.2477</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>-0.0445</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>139.65</v>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>2분기 매출 78.1억달러로 예상치 상회했으나 AI 설비투자 급증(183.7억달러)으로 시간외 주가 8% 급락. 베트남 위성 발사 계약 체결.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>Redwire Corp</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>RDW</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
+          <t>Redwire Corporation</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
         <v>0.1568</v>
       </c>
-      <c r="D12" s="11" t="n">
-        <v>-0.0808</v>
-      </c>
-      <c r="E12" s="12" t="n">
+      <c r="C8" s="8" t="n">
+        <v>-0.080801</v>
+      </c>
+      <c r="D8" s="9" t="n">
         <v>12.4</v>
       </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>2분기 매출 1.171억달러로 예상치 상회, 국방용 Stalker UAS 추가 수주(2,150만달러). 실적 발표일 주가 12.85% 급등 후 이번 주 조정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Rocket Lab Corp</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>RKLB</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="n">
+      <c r="E8" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>카네마츠와 협력 계약 체결(8/17), 2분기 매출 컨센서스 상회에도 최근 주가는 약세 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Rocket Lab Corporation</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
         <v>0.144</v>
       </c>
-      <c r="D13" s="11" t="n">
-        <v>-0.06570000000000001</v>
-      </c>
-      <c r="E13" s="12" t="n">
+      <c r="C9" s="8" t="n">
+        <v>-0.065665</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>75.84</v>
       </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>2분기 손실폭이 예상보다 커 주가 하락. 다만 이리디움 인수 관련 반독점 심사(HSR) 통과, 우주군 신규 계약으로 펀더멘털은 양호.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Intuitive Machines Inc</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>LUNR</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="n">
+      <c r="E9" s="10" t="n">
+        <v>484.9</v>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>美우주군 NITE-STAR·SDN 컨소시엄 추가 선정, MDA向 위성 8기 발사 성공, 이리듐 인수 절차(HSR 만료·S-4 제출) 진행</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Intuitive Machines, Inc.</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
         <v>0.1296</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>0.0926</v>
-      </c>
-      <c r="E14" s="12" t="n">
+      <c r="C10" s="8" t="n">
+        <v>0.092625</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>18.52</v>
       </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>임무 차질 우려로 실적 발표 직후 급락했으나 6억달러 규모 위성통신 인프라 수주 소식에 급반등. 수주잔고 18억달러로 사상 최대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>EchoStar Corp</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>ECHO</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="n">
+      <c r="E10" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>L3Harris向 미사일방어 위성 18기 공급계약, 6억달러 이상 통신위성 프로그램 착수 승인으로 백로그 18억달러로 확대</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>EchoStar Corporation</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
         <v>0.08960000000000001</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>-0.04389999999999999</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>88.44</v>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>2분기 매출 35.8억달러로 전년比 감소. 자회사 휴즈네트웍스 파산 신청 및 임원 사임 등 구조조정 이슈로 주가 압박.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>AST SpaceMobile Inc</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t>ASTS</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="n">
+      <c r="C11" s="8" t="n">
+        <v>-0.043892</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>88.435</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>256.9</v>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>자회사 휴즈네트웍스 15억달러 채무 만기(8/1) 관련 구조조정 절차 진행 중, 2분기 매출은 전년比 소폭 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>AST SpaceMobile, Inc.</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
         <v>0.06950000000000001</v>
       </c>
-      <c r="D16" s="11" t="n">
-        <v>-0.106</v>
-      </c>
-      <c r="E16" s="12" t="n">
+      <c r="C12" s="8" t="n">
+        <v>-0.106042</v>
+      </c>
+      <c r="D12" s="9" t="n">
         <v>66.43000000000001</v>
       </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>신형 블루버드 위성 3기 팰컨9 발사 성공했으나 2분기 매출이 예상치 하회, BofA·UBS 목표주가 하향으로 주가 큰 폭 하락.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="E12" s="10" t="n">
+        <v>258.5</v>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
+        <is>
+          <t>2분기 매출 컨센서스 하회·손실 확대 및 전환사채 발행 관련 희석 우려로 주가 약세 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Planet Labs PBC</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="n">
+      <c r="B13" s="7" t="n">
         <v>0.0645</v>
       </c>
-      <c r="D17" s="11" t="n">
-        <v>-0.0767</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="C13" s="8" t="n">
+        <v>-0.076735</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>22.62</v>
       </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>우주 관련주 전반의 조정 속 주가 약세. 영국·독일 신규 사업 확장 소식은 긍정적이나 밸류에이션 부담 지속.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Voyager Technologies Inc</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>VOYG</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="n">
+      <c r="E13" s="10" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
+        <is>
+          <t>국채금리 상승·반도체株 급락에 따른 우주株 전반 조정에 동반 하락, 스코틀랜드 AI 모니터링 계약 등은 긍정적</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Voyager Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
         <v>0.0336</v>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>-0.0965</v>
-      </c>
-      <c r="E18" s="12" t="n">
+      <c r="C14" s="8" t="n">
+        <v>-0.09651199999999999</v>
+      </c>
+      <c r="D14" s="9" t="n">
         <v>38.85</v>
       </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>2분기 매출 5,270만달러로 사상 최대, 우주군 위성통신 계약 수주 및 연간 가이던스 상향에도 이번 주 큰 폭 조정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>MDA Space Ltd</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>MDA</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="n">
+      <c r="E14" s="10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>2분기 매출 5,275만달러(전년比 +15.5%)로 사상 최대, 2026년 매출 가이던스 상향(2.75~3.05억달러)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>MDA Space Ltd.</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
         <v>0.0332</v>
       </c>
-      <c r="D19" s="11" t="n">
-        <v>-0.0898</v>
-      </c>
-      <c r="E19" s="12" t="n">
+      <c r="C15" s="8" t="n">
+        <v>-0.08981199999999999</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>32.43</v>
       </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>2분기 매출 캐나다달러 4.966억으로 예상치 상회, 실적 호조로 급등했던 주가가 이번 주 상당폭 조정. 모건스탠리 매수 의견 유지.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Firefly Aerospace Inc</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>FLY</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="n">
+      <c r="E15" s="10" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>텔레샛向 AURORA 위성 추가 공급계약, 글로벌스타 재보충위성 8기 궤도 안착, 2분기 매출 전년比 34%↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Firefly Aerospace Inc.</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>0.0312</v>
       </c>
-      <c r="D20" s="11" t="n">
-        <v>-0.0467</v>
-      </c>
-      <c r="E20" s="12" t="n">
+      <c r="C16" s="8" t="n">
+        <v>-0.046722</v>
+      </c>
+      <c r="D16" s="9" t="n">
         <v>25.3</v>
       </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>2분기 매출 1.177억달러로 전년比 659% 급증, 엔비디아 협업·NASA 및 국방 계약 확대에도 이번 주 소폭 조정.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>출처: 편입종목·비중 - 미래에셋자산운용 TIGER ETF 월간 팩트시트(2026-07-31 기준, investments.miraeasset.com); 주가 - Yahoo Finance(via yfinance 대체 조회, 2026-08-12~2026-08-19 종가); 이슈 요약 - 각 사 최근 7일 내 공개 뉴스</t>
+      <c r="E16" s="10" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>록히드마틴과 계약 2031년까지 연장(8/17), Elytra 궤도이탈 서비스 설계계약 수주, 2분기 매출 전년比 659%↑</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>자료: 미래에셋자산운용 TIGER ETF 월간운용보고서(FactSheet, 2026년 7월 31일 기준, https://investments.miraeasset.com/tigeretf), Yahoo Finance(주가·시가총액, 2026-08-19 기준). 비중 합계는 반올림으로 100%와 소폭 차이가 있을 수 있음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
-  <conditionalFormatting sqref="D11:D20">
+  <conditionalFormatting sqref="C7:C16">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>

--- a/reports/2026-08-20-tiger-space-etf-weekly.xlsx
+++ b/reports/2026-08-20-tiger-space-etf-weekly.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주간보고서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Space ETF 주간리포트" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -51,15 +51,15 @@
     </font>
     <font>
       <name val="Noto Sans KR"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Noto Sans KR"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Noto Sans KR"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,27 +76,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -116,28 +102,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -521,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -546,310 +532,320 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>이번 주 상승 상위: Intuitive Machines(LUNR) +9.26%</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>이번 주 하락 상위 3개: AST SpaceMobile(ASTS) -10.60%, Voyager Technologies(VOYG) -9.65%, MDA Space(MDA) -8.98%</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="8" customHeight="1"/>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>비중(%)</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>이번주 등락률(%)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>종가(USD)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>시가총액(억달러)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>주요 이슈</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Space Exploration Technologies Corp.</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>0.2477</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>-0.044475</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>139.65</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>18408.4</v>
-      </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>글로벌스타·美우주군 위성 연속 발사(38분 간격 신기록), 2026년 100번째 미션 달성 등 팰컨9 발사 랠리 지속</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Redwire Corporation</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n">
-        <v>0.1568</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>-0.080801</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>31</v>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>카네마츠와 협력 계약 체결(8/17), 2분기 매출 컨센서스 상회에도 최근 주가는 약세 지속</t>
-        </is>
-      </c>
-    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>조사 대상 10종목 중 상승 종목이 1개뿐이라 상승 상위는 1건만 표기함 (나머지 9개 종목은 모두 하락).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="8" customHeight="1"/>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>비중(%)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>이번주 등락률(%)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>종가(USD)</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>시가총액(억달러)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>주요 이슈</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Space Exploration Technologies Corp.</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>-0.044475</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>139.65</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>18408.4</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>글로벌스타·美우주군 위성 연속 발사(38분 간격 신기록), 2026년 100번째 미션 달성 등 팰컨9 발사 랠리 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Redwire Corporation</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0.1568</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>-0.080801</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>카네마츠와 협력 계약 체결(8/17), 2분기 매출 컨센서스 상회에도 최근 주가는 약세 지속</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
           <t>Rocket Lab Corporation</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n">
+      <c r="B12" s="8" t="n">
         <v>0.144</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C12" s="9" t="n">
         <v>-0.065665</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D12" s="10" t="n">
         <v>75.84</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>484.9</v>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>美우주군 NITE-STAR·SDN 컨소시엄 추가 선정, MDA向 위성 8기 발사 성공, 이리듐 인수 절차(HSR 만료·S-4 제출) 진행</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Intuitive Machines, Inc.</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B13" s="8" t="n">
         <v>0.1296</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <v>0.092625</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D13" s="10" t="n">
         <v>18.52</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E13" s="11" t="n">
         <v>29.7</v>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>L3Harris向 미사일방어 위성 18기 공급계약, 6억달러 이상 통신위성 프로그램 착수 승인으로 백로그 18억달러로 확대</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>EchoStar Corporation</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>0.08960000000000001</v>
-      </c>
-      <c r="C11" s="8" t="n">
+      <c r="B14" s="8" t="n">
+        <v>0.0896</v>
+      </c>
+      <c r="C14" s="9" t="n">
         <v>-0.043892</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D14" s="10" t="n">
         <v>88.435</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <v>256.9</v>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>자회사 휴즈네트웍스 15억달러 채무 만기(8/1) 관련 구조조정 절차 진행 중, 2분기 매출은 전년比 소폭 감소</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>AST SpaceMobile, Inc.</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B15" s="8" t="n">
         <v>0.06950000000000001</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C15" s="9" t="n">
         <v>-0.106042</v>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D15" s="10" t="n">
         <v>66.43000000000001</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E15" s="11" t="n">
         <v>258.5</v>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>2분기 매출 컨센서스 하회·손실 확대 및 전환사채 발행 관련 희석 우려로 주가 약세 지속</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Planet Labs PBC</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n">
+      <c r="B16" s="8" t="n">
         <v>0.0645</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C16" s="9" t="n">
         <v>-0.076735</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D16" s="10" t="n">
         <v>22.62</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E16" s="11" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>국채금리 상승·반도체株 급락에 따른 우주株 전반 조정에 동반 하락, 스코틀랜드 AI 모니터링 계약 등은 긍정적</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Voyager Technologies, Inc.</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B17" s="8" t="n">
         <v>0.0336</v>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>-0.09651199999999999</v>
-      </c>
-      <c r="D14" s="9" t="n">
+      <c r="C17" s="9" t="n">
+        <v>-0.096512</v>
+      </c>
+      <c r="D17" s="10" t="n">
         <v>38.85</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E17" s="11" t="n">
         <v>23.5</v>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>2분기 매출 5,275만달러(전년比 +15.5%)로 사상 최대, 2026년 매출 가이던스 상향(2.75~3.05억달러)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>MDA Space Ltd.</t>
         </is>
       </c>
-      <c r="B15" s="7" t="n">
+      <c r="B18" s="8" t="n">
         <v>0.0332</v>
       </c>
-      <c r="C15" s="8" t="n">
-        <v>-0.08981199999999999</v>
-      </c>
-      <c r="D15" s="9" t="n">
+      <c r="C18" s="9" t="n">
+        <v>-0.089812</v>
+      </c>
+      <c r="D18" s="10" t="n">
         <v>32.43</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E18" s="11" t="n">
         <v>52.6</v>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>텔레샛向 AURORA 위성 추가 공급계약, 글로벌스타 재보충위성 8기 궤도 안착, 2분기 매출 전년比 34%↑</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Firefly Aerospace Inc.</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <v>0.0312</v>
       </c>
-      <c r="C16" s="8" t="n">
+      <c r="C19" s="9" t="n">
         <v>-0.046722</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D19" s="10" t="n">
         <v>25.3</v>
       </c>
-      <c r="E16" s="10" t="n">
+      <c r="E19" s="11" t="n">
         <v>42.4</v>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>록히드마틴과 계약 2031년까지 연장(8/17), Elytra 궤도이탈 서비스 설계계약 수주, 2분기 매출 전년比 659%↑</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>자료: 미래에셋자산운용 TIGER ETF 월간운용보고서(FactSheet, 2026년 7월 31일 기준, https://investments.miraeasset.com/tigeretf), Yahoo Finance(주가·시가총액, 2026-08-19 기준). 비중 합계는 반올림으로 100%와 소폭 차이가 있을 수 있음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
-  <conditionalFormatting sqref="C7:C16">
+  <conditionalFormatting sqref="C10:C19">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
